--- a/data/trans_bre/IP16B04-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16B04-Clase-trans_bre.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -746,7 +746,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Grupo IV y V</t>
+          <t>Grupo VI</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -841,14 +841,14 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -856,12 +856,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Grupo VII</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -986,7 +986,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>No ha trabajado</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1064,101 +1064,20 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A14:A15"/>
